--- a/docs/Unit_Test_Cases.xlsx
+++ b/docs/Unit_Test_Cases.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" r:id="R1cfe3aacffa045b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" r:id="R2633a8f540f646a1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitTestCasesTable" displayName="UnitTestCasesTable" ref="A4:I55" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="UnitTestCasesTable" displayName="UnitTestCasesTable" ref="A4:I63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="Test Case ID"/>
     <x:tableColumn id="2" name="Module"/>
@@ -445,8 +445,8 @@
         <x:v>Recorded test cases</x:v>
       </x:c>
       <x:c r="B3" s="11" t="n">
-        <x:f>COUNTA(A5:A55)</x:f>
-        <x:v>51</x:v>
+        <x:f>COUNTA(A5:A63)</x:f>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C3" s="12" t="str">
         <x:v>Source of truth</x:v>
@@ -1274,28 +1274,28 @@
     </x:row>
     <x:row r="32" ht="62" customHeight="1">
       <x:c r="A32" s="16" t="str">
-        <x:v>UT-EXT-001</x:v>
+        <x:v>UT-NRM-006</x:v>
       </x:c>
       <x:c r="B32" s="16" t="str">
-        <x:v>Meeting extraction</x:v>
+        <x:v>Transcript normalization</x:v>
       </x:c>
       <x:c r="C32" s="16" t="str">
-        <x:v>Duplicate participants and topics</x:v>
+        <x:v>Rough-note bullet separation</x:v>
       </x:c>
       <x:c r="D32" s="16" t="str">
-        <x:v>Repeated speakers and two subject areas</x:v>
+        <x:v>English notes contain metadata and bullet points but no speaker labels</x:v>
       </x:c>
       <x:c r="E32" s="16" t="str">
-        <x:v>Release and infrastructure fixture</x:v>
+        <x:v>Instructor rough-note fixture</x:v>
       </x:c>
       <x:c r="F32" s="16" t="str">
-        <x:v>Normalize and extract meeting.</x:v>
+        <x:v>Normalize transcript; inspect kinds and speakers.</x:v>
       </x:c>
       <x:c r="G32" s="16" t="str">
-        <x:v>Participants are deduplicated and topics remain separate.</x:v>
+        <x:v>Bullets remain separate notes, metadata is typed separately, and no metadata label becomes a speaker.</x:v>
       </x:c>
       <x:c r="H32" s="16" t="str">
-        <x:v>tests/unit/extractor.test.ts — deduplicates participants and separates release and infrastructure topics</x:v>
+        <x:v>tests/unit/normalizer.test.ts — keeps rough-note bullets separate instead of treating metadata as a speaker</x:v>
       </x:c>
       <x:c r="I32" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1303,28 +1303,28 @@
     </x:row>
     <x:row r="33" ht="62" customHeight="1">
       <x:c r="A33" s="16" t="str">
-        <x:v>UT-EXT-002</x:v>
+        <x:v>UT-NRM-007</x:v>
       </x:c>
       <x:c r="B33" s="16" t="str">
-        <x:v>Meeting extraction</x:v>
+        <x:v>Transcript normalization</x:v>
       </x:c>
       <x:c r="C33" s="16" t="str">
-        <x:v>No invented participants</x:v>
+        <x:v>Markdown sections with metadata</x:v>
       </x:c>
       <x:c r="D33" s="16" t="str">
-        <x:v>Unlabelled transcript</x:v>
+        <x:v>Structured notes mix headings, attendee metadata, bullets, and speaker lines</x:v>
       </x:c>
       <x:c r="E33" s="16" t="str">
-        <x:v>Ownerless requirement</x:v>
+        <x:v>Instructor structured-followups fixture</x:v>
       </x:c>
       <x:c r="F33" s="16" t="str">
-        <x:v>Extract meeting.</x:v>
+        <x:v>Normalize transcript; inspect heading, note, metadata, and speech kinds.</x:v>
       </x:c>
       <x:c r="G33" s="16" t="str">
-        <x:v>Participants list is empty.</x:v>
+        <x:v>Only actual speakers are labeled; section headings and parking-lot bullets remain distinct evidence.</x:v>
       </x:c>
       <x:c r="H33" s="16" t="str">
-        <x:v>tests/unit/extractor.test.ts — does not invent participants for unlabelled content</x:v>
+        <x:v>tests/unit/normalizer.test.ts — distinguishes Markdown sections and metadata from real speakers</x:v>
       </x:c>
       <x:c r="I33" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1332,28 +1332,28 @@
     </x:row>
     <x:row r="34" ht="62" customHeight="1">
       <x:c r="A34" s="16" t="str">
-        <x:v>UT-EXT-003</x:v>
+        <x:v>UT-NRM-008</x:v>
       </x:c>
       <x:c r="B34" s="16" t="str">
-        <x:v>Meeting extraction</x:v>
+        <x:v>Transcript normalization</x:v>
       </x:c>
       <x:c r="C34" s="16" t="str">
-        <x:v>Structured empty result</x:v>
+        <x:v>Thai metadata labels</x:v>
       </x:c>
       <x:c r="D34" s="16" t="str">
-        <x:v>Empty normalized transcript</x:v>
+        <x:v>Thai transcript includes date and participant metadata before dialogue</x:v>
       </x:c>
       <x:c r="E34" s="16" t="str">
-        <x:v>Empty text</x:v>
+        <x:v>Instructor Thai conflict fixture</x:v>
       </x:c>
       <x:c r="F34" s="16" t="str">
-        <x:v>Extract meeting.</x:v>
+        <x:v>Normalize transcript; inspect speakers and metadata kinds.</x:v>
       </x:c>
       <x:c r="G34" s="16" t="str">
-        <x:v>Valid result with empty-transcript flag is returned.</x:v>
+        <x:v>Thai metadata labels are not returned as speakers; the four dialogue speakers remain available.</x:v>
       </x:c>
       <x:c r="H34" s="16" t="str">
-        <x:v>tests/unit/extractor.test.ts — returns a structured empty analysis instead of throwing</x:v>
+        <x:v>tests/unit/normalizer.test.ts — does not add Thai date and attendee labels as participants</x:v>
       </x:c>
       <x:c r="I34" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1361,28 +1361,28 @@
     </x:row>
     <x:row r="35" ht="62" customHeight="1">
       <x:c r="A35" s="16" t="str">
-        <x:v>UT-EXT-004</x:v>
+        <x:v>UT-INS-001</x:v>
       </x:c>
       <x:c r="B35" s="16" t="str">
-        <x:v>Meeting extraction</x:v>
+        <x:v>Instructor regression</x:v>
       </x:c>
       <x:c r="C35" s="16" t="str">
-        <x:v>Malformed control characters</x:v>
+        <x:v>English unresolved brainstorm</x:v>
       </x:c>
       <x:c r="D35" s="16" t="str">
-        <x:v>Text includes controls</x:v>
+        <x:v>Rough notes contain mobile/API alternatives and no final priority</x:v>
       </x:c>
       <x:c r="E35" s="16" t="str">
-        <x:v>Malformed control-character content</x:v>
+        <x:v>instructor-01-no-decisions-brainstorm.txt</x:v>
       </x:c>
       <x:c r="F35" s="16" t="str">
-        <x:v>Normalize and extract.</x:v>
+        <x:v>Normalize and extract the complete meeting.</x:v>
       </x:c>
       <x:c r="G35" s="16" t="str">
-        <x:v>Pipeline does not crash and retains usable text.</x:v>
+        <x:v>Sam and Lena are participants; no decision is invented; one unassigned mobile-churn action and no-decision warning are returned.</x:v>
       </x:c>
       <x:c r="H35" s="16" t="str">
-        <x:v>tests/unit/extractor.test.ts — handles malformed control characters without crashing</x:v>
+        <x:v>tests/unit/instructor-samples.test.ts — extracts unresolved product planning from the English rough notes without a false decision</x:v>
       </x:c>
       <x:c r="I35" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1390,28 +1390,28 @@
     </x:row>
     <x:row r="36" ht="62" customHeight="1">
       <x:c r="A36" s="16" t="str">
-        <x:v>UT-SCH-001</x:v>
+        <x:v>UT-INS-002</x:v>
       </x:c>
       <x:c r="B36" s="16" t="str">
-        <x:v>Shared contracts</x:v>
+        <x:v>Instructor regression</x:v>
       </x:c>
       <x:c r="C36" s="16" t="str">
-        <x:v>Valid structured analysis</x:v>
+        <x:v>Structured engineering follow-ups</x:v>
       </x:c>
       <x:c r="D36" s="16" t="str">
-        <x:v>Complete analysis object</x:v>
+        <x:v>Markdown notes contain explicit topics, decisions, owners, dates, and a parking lot</x:v>
       </x:c>
       <x:c r="E36" s="16" t="str">
-        <x:v>Typed meeting result</x:v>
+        <x:v>instructor-02-structured-with-followups.txt</x:v>
       </x:c>
       <x:c r="F36" s="16" t="str">
-        <x:v>Parse with Zod schema.</x:v>
+        <x:v>Normalize and extract the complete meeting.</x:v>
       </x:c>
       <x:c r="G36" s="16" t="str">
-        <x:v>Schema accepts the result.</x:v>
+        <x:v>Four participants, section topics, two decisions, four exact follow-up actions, and a parking-lot no-decision warning are returned.</x:v>
       </x:c>
       <x:c r="H36" s="16" t="str">
-        <x:v>tests/unit/contracts.test.ts — accepts a complete evidence-bound meeting result</x:v>
+        <x:v>tests/unit/instructor-samples.test.ts — extracts section topics, final decisions, and four follow-up actions from structured notes</x:v>
       </x:c>
       <x:c r="I36" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1419,28 +1419,28 @@
     </x:row>
     <x:row r="37" ht="62" customHeight="1">
       <x:c r="A37" s="16" t="str">
-        <x:v>UT-SCH-002</x:v>
+        <x:v>UT-INS-003</x:v>
       </x:c>
       <x:c r="B37" s="16" t="str">
-        <x:v>Shared contracts</x:v>
+        <x:v>Instructor regression</x:v>
       </x:c>
       <x:c r="C37" s="16" t="str">
-        <x:v>Invalid empty action task</x:v>
+        <x:v>Thai unresolved roadmap</x:v>
       </x:c>
       <x:c r="D37" s="16" t="str">
-        <x:v>Action object has no task</x:v>
+        <x:v>Thai rough notes discuss mobile/API options without resolution</x:v>
       </x:c>
       <x:c r="E37" s="16" t="str">
-        <x:v>Empty task string</x:v>
+        <x:v>instructor-03-thai-no-decisions-roadmap.txt</x:v>
       </x:c>
       <x:c r="F37" s="16" t="str">
-        <x:v>Parse with Zod schema.</x:v>
+        <x:v>Normalize and extract the complete meeting.</x:v>
       </x:c>
       <x:c r="G37" s="16" t="str">
-        <x:v>Schema rejects the action.</x:v>
+        <x:v>Two evidence-backed participants, one unassigned churn-data action, no invented decision, and no-decision warning are returned.</x:v>
       </x:c>
       <x:c r="H37" s="16" t="str">
-        <x:v>tests/unit/contracts.test.ts — rejects action items without a task</x:v>
+        <x:v>tests/unit/instructor-samples.test.ts — extracts Thai rough-note participants and unresolved work without inventing a decision</x:v>
       </x:c>
       <x:c r="I37" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1448,28 +1448,28 @@
     </x:row>
     <x:row r="38" ht="62" customHeight="1">
       <x:c r="A38" s="16" t="str">
-        <x:v>IT-API-001</x:v>
+        <x:v>UT-INS-004</x:v>
       </x:c>
       <x:c r="B38" s="16" t="str">
-        <x:v>Analysis API</x:v>
+        <x:v>Instructor regression</x:v>
       </x:c>
       <x:c r="C38" s="16" t="str">
-        <x:v>Analyze one transcript</x:v>
+        <x:v>Thai launch and freeze conflict</x:v>
       </x:c>
       <x:c r="D38" s="16" t="str">
-        <x:v>Express app is available</x:v>
+        <x:v>Thai dialogue contains a launch resolution plus unresolved public-date and freeze/dashboard contradictions</x:v>
       </x:c>
       <x:c r="E38" s="16" t="str">
-        <x:v>format-a.txt multipart upload</x:v>
+        <x:v>instructor-04-thai-conflicting-launch.txt</x:v>
       </x:c>
       <x:c r="F38" s="16" t="str">
-        <x:v>POST /api/analyze.</x:v>
+        <x:v>Normalize and extract the complete meeting.</x:v>
       </x:c>
       <x:c r="G38" s="16" t="str">
-        <x:v>Structured meeting, participants, topics, actions, and groups are returned.</x:v>
+        <x:v>Four participants, launch/dashboard decisions, two actions, explicit unresolved evidence, and both launch-date and freeze conflicts are returned.</x:v>
       </x:c>
       <x:c r="H38" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — analyzes one transcript into structured results</x:v>
+        <x:v>tests/unit/instructor-samples.test.ts — retains the Thai launch resolution while flagging unresolved launch and freeze conflicts</x:v>
       </x:c>
       <x:c r="I38" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1477,28 +1477,28 @@
     </x:row>
     <x:row r="39" ht="62" customHeight="1">
       <x:c r="A39" s="16" t="str">
-        <x:v>IT-API-000</x:v>
+        <x:v>UT-EXT-001</x:v>
       </x:c>
       <x:c r="B39" s="16" t="str">
-        <x:v>Analysis API</x:v>
+        <x:v>Meeting extraction</x:v>
       </x:c>
       <x:c r="C39" s="16" t="str">
-        <x:v>No-file request</x:v>
+        <x:v>Duplicate participants and topics</x:v>
       </x:c>
       <x:c r="D39" s="16" t="str">
-        <x:v>Express app is available</x:v>
+        <x:v>Repeated speakers and two subject areas</x:v>
       </x:c>
       <x:c r="E39" s="16" t="str">
-        <x:v>Multipart request without files</x:v>
+        <x:v>Release and infrastructure fixture</x:v>
       </x:c>
       <x:c r="F39" s="16" t="str">
-        <x:v>POST /api/analyze.</x:v>
+        <x:v>Normalize and extract meeting.</x:v>
       </x:c>
       <x:c r="G39" s="16" t="str">
-        <x:v>HTTP 400 returns a safe prompt to select a transcript.</x:v>
+        <x:v>Participants are deduplicated and topics remain separate.</x:v>
       </x:c>
       <x:c r="H39" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — rejects requests without files using a safe client message</x:v>
+        <x:v>tests/unit/extractor.test.ts — deduplicates participants and separates release and infrastructure topics</x:v>
       </x:c>
       <x:c r="I39" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1506,28 +1506,28 @@
     </x:row>
     <x:row r="40" ht="62" customHeight="1">
       <x:c r="A40" s="16" t="str">
-        <x:v>IT-API-002</x:v>
+        <x:v>UT-EXT-002</x:v>
       </x:c>
       <x:c r="B40" s="16" t="str">
-        <x:v>Analysis API</x:v>
+        <x:v>Meeting extraction</x:v>
       </x:c>
       <x:c r="C40" s="16" t="str">
-        <x:v>Partial batch failure</x:v>
+        <x:v>No invented participants</x:v>
       </x:c>
       <x:c r="D40" s="16" t="str">
-        <x:v>Valid TXT and unsupported file</x:v>
+        <x:v>Unlabelled transcript</x:v>
       </x:c>
       <x:c r="E40" s="16" t="str">
-        <x:v>Two multipart files</x:v>
+        <x:v>Ownerless requirement</x:v>
       </x:c>
       <x:c r="F40" s="16" t="str">
-        <x:v>POST /api/analyze.</x:v>
+        <x:v>Extract meeting.</x:v>
       </x:c>
       <x:c r="G40" s="16" t="str">
-        <x:v>Valid result is preserved and unsupported file is reported independently.</x:v>
+        <x:v>Participants list is empty.</x:v>
       </x:c>
       <x:c r="H40" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — preserves valid results when another uploaded file is unsupported</x:v>
+        <x:v>tests/unit/extractor.test.ts — does not invent participants for unlabelled content</x:v>
       </x:c>
       <x:c r="I40" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1535,28 +1535,28 @@
     </x:row>
     <x:row r="41" ht="62" customHeight="1">
       <x:c r="A41" s="16" t="str">
-        <x:v>IT-API-003</x:v>
+        <x:v>UT-EXT-003</x:v>
       </x:c>
       <x:c r="B41" s="16" t="str">
-        <x:v>Analysis API</x:v>
+        <x:v>Meeting extraction</x:v>
       </x:c>
       <x:c r="C41" s="16" t="str">
-        <x:v>Empty file isolation</x:v>
+        <x:v>Structured empty result</x:v>
       </x:c>
       <x:c r="D41" s="16" t="str">
-        <x:v>Valid TXT and empty TXT</x:v>
+        <x:v>Empty normalized transcript</x:v>
       </x:c>
       <x:c r="E41" s="16" t="str">
-        <x:v>Two multipart files</x:v>
+        <x:v>Empty text</x:v>
       </x:c>
       <x:c r="F41" s="16" t="str">
-        <x:v>POST /api/analyze.</x:v>
+        <x:v>Extract meeting.</x:v>
       </x:c>
       <x:c r="G41" s="16" t="str">
-        <x:v>Valid meeting succeeds and empty file has its own failure.</x:v>
+        <x:v>Valid result with empty-transcript flag is returned.</x:v>
       </x:c>
       <x:c r="H41" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — reports an empty file independently while processing another file</x:v>
+        <x:v>tests/unit/extractor.test.ts — returns a structured empty analysis instead of throwing</x:v>
       </x:c>
       <x:c r="I41" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1564,28 +1564,28 @@
     </x:row>
     <x:row r="42" ht="62" customHeight="1">
       <x:c r="A42" s="16" t="str">
-        <x:v>IT-API-004</x:v>
+        <x:v>UT-EXT-004</x:v>
       </x:c>
       <x:c r="B42" s="16" t="str">
-        <x:v>Analysis API</x:v>
+        <x:v>Meeting extraction</x:v>
       </x:c>
       <x:c r="C42" s="16" t="str">
-        <x:v>Health endpoint</x:v>
+        <x:v>Malformed control characters</x:v>
       </x:c>
       <x:c r="D42" s="16" t="str">
-        <x:v>Express app is available</x:v>
+        <x:v>Text includes controls</x:v>
       </x:c>
       <x:c r="E42" s="16" t="str">
-        <x:v>GET /api/health</x:v>
+        <x:v>Malformed control-character content</x:v>
       </x:c>
       <x:c r="F42" s="16" t="str">
-        <x:v>Request service readiness.</x:v>
+        <x:v>Normalize and extract.</x:v>
       </x:c>
       <x:c r="G42" s="16" t="str">
-        <x:v>HTTP 200 reports ready without internal implementation details.</x:v>
+        <x:v>Pipeline does not crash and retains usable text.</x:v>
       </x:c>
       <x:c r="H42" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — reports service readiness without exposing internals</x:v>
+        <x:v>tests/unit/extractor.test.ts — handles malformed control characters without crashing</x:v>
       </x:c>
       <x:c r="I42" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1593,28 +1593,28 @@
     </x:row>
     <x:row r="43" ht="62" customHeight="1">
       <x:c r="A43" s="16" t="str">
-        <x:v>IT-API-005</x:v>
+        <x:v>UT-SCH-001</x:v>
       </x:c>
       <x:c r="B43" s="16" t="str">
-        <x:v>Analysis API</x:v>
+        <x:v>Shared contracts</x:v>
       </x:c>
       <x:c r="C43" s="16" t="str">
-        <x:v>Oversized file isolation</x:v>
+        <x:v>Valid structured analysis</x:v>
       </x:c>
       <x:c r="D43" s="16" t="str">
-        <x:v>Valid TXT and a TXT over 1 MiB</x:v>
+        <x:v>Complete analysis object</x:v>
       </x:c>
       <x:c r="E43" s="16" t="str">
-        <x:v>Two multipart files</x:v>
+        <x:v>Typed meeting result</x:v>
       </x:c>
       <x:c r="F43" s="16" t="str">
-        <x:v>POST /api/analyze.</x:v>
+        <x:v>Parse with Zod schema.</x:v>
       </x:c>
       <x:c r="G43" s="16" t="str">
-        <x:v>Valid meeting succeeds and oversized file receives file-too-large failure.</x:v>
+        <x:v>Schema accepts the result.</x:v>
       </x:c>
       <x:c r="H43" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — keeps valid results when another text file exceeds the application limit</x:v>
+        <x:v>tests/unit/contracts.test.ts — accepts a complete evidence-bound meeting result</x:v>
       </x:c>
       <x:c r="I43" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1622,28 +1622,28 @@
     </x:row>
     <x:row r="44" ht="62" customHeight="1">
       <x:c r="A44" s="16" t="str">
-        <x:v>IT-API-006</x:v>
+        <x:v>UT-SCH-002</x:v>
       </x:c>
       <x:c r="B44" s="16" t="str">
-        <x:v>Analysis API</x:v>
+        <x:v>Shared contracts</x:v>
       </x:c>
       <x:c r="C44" s="16" t="str">
-        <x:v>Invalid UTF-8 isolation</x:v>
+        <x:v>Invalid empty action task</x:v>
       </x:c>
       <x:c r="D44" s="16" t="str">
-        <x:v>Valid TXT and invalid byte sequence</x:v>
+        <x:v>Action object has no task</x:v>
       </x:c>
       <x:c r="E44" s="16" t="str">
-        <x:v>Two multipart files</x:v>
+        <x:v>Empty task string</x:v>
       </x:c>
       <x:c r="F44" s="16" t="str">
-        <x:v>POST /api/analyze.</x:v>
+        <x:v>Parse with Zod schema.</x:v>
       </x:c>
       <x:c r="G44" s="16" t="str">
-        <x:v>Valid meeting succeeds and invalid text receives invalid-upload failure.</x:v>
+        <x:v>Schema rejects the action.</x:v>
       </x:c>
       <x:c r="H44" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — reports invalid UTF-8 as a per-file upload failure</x:v>
+        <x:v>tests/unit/contracts.test.ts — rejects action items without a task</x:v>
       </x:c>
       <x:c r="I44" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1651,28 +1651,28 @@
     </x:row>
     <x:row r="45" ht="62" customHeight="1">
       <x:c r="A45" s="16" t="str">
-        <x:v>IT-API-007</x:v>
+        <x:v>IT-API-001</x:v>
       </x:c>
       <x:c r="B45" s="16" t="str">
         <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C45" s="16" t="str">
-        <x:v>Prototype-safe owner grouping</x:v>
+        <x:v>Analyze one transcript</x:v>
       </x:c>
       <x:c r="D45" s="16" t="str">
-        <x:v>Owner name is Constructor</x:v>
+        <x:v>Express app is available</x:v>
       </x:c>
       <x:c r="E45" s="16" t="str">
-        <x:v>Constructor: I will prepare the release notes Friday.</x:v>
+        <x:v>format-a.txt multipart upload</x:v>
       </x:c>
       <x:c r="F45" s="16" t="str">
-        <x:v>POST /api/analyze; inspect groupedActionItems.</x:v>
+        <x:v>POST /api/analyze.</x:v>
       </x:c>
       <x:c r="G45" s="16" t="str">
-        <x:v>Constructor group contains the action and request succeeds.</x:v>
+        <x:v>Structured meeting, participants, topics, actions, and groups are returned.</x:v>
       </x:c>
       <x:c r="H45" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — groups an owner whose name matches an object prototype property</x:v>
+        <x:v>tests/api/analyze-api.test.ts — analyzes one transcript into structured results</x:v>
       </x:c>
       <x:c r="I45" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1680,28 +1680,28 @@
     </x:row>
     <x:row r="46" ht="62" customHeight="1">
       <x:c r="A46" s="16" t="str">
-        <x:v>IT-API-008</x:v>
+        <x:v>IT-API-000</x:v>
       </x:c>
       <x:c r="B46" s="16" t="str">
-        <x:v>HTTP boundary</x:v>
+        <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C46" s="16" t="str">
-        <x:v>Same-origin policy</x:v>
+        <x:v>No-file request</x:v>
       </x:c>
       <x:c r="D46" s="16" t="str">
-        <x:v>Health endpoint available</x:v>
+        <x:v>Express app is available</x:v>
       </x:c>
       <x:c r="E46" s="16" t="str">
-        <x:v>GET with attacker Origin header</x:v>
+        <x:v>Multipart request without files</x:v>
       </x:c>
       <x:c r="F46" s="16" t="str">
-        <x:v>Request /api/health.</x:v>
+        <x:v>POST /api/analyze.</x:v>
       </x:c>
       <x:c r="G46" s="16" t="str">
-        <x:v>Response does not grant Access-Control-Allow-Origin.</x:v>
+        <x:v>HTTP 400 returns a safe prompt to select a transcript.</x:v>
       </x:c>
       <x:c r="H46" s="16" t="str">
-        <x:v>tests/api/analyze-api.test.ts — does not opt arbitrary third-party origins into CORS</x:v>
+        <x:v>tests/api/analyze-api.test.ts — rejects requests without files using a safe client message</x:v>
       </x:c>
       <x:c r="I46" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1709,28 +1709,28 @@
     </x:row>
     <x:row r="47" ht="62" customHeight="1">
       <x:c r="A47" s="16" t="str">
-        <x:v>IT-RPT-000</x:v>
+        <x:v>IT-API-002</x:v>
       </x:c>
       <x:c r="B47" s="16" t="str">
-        <x:v>Report API</x:v>
+        <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C47" s="16" t="str">
-        <x:v>Malformed report request</x:v>
+        <x:v>Partial batch failure</x:v>
       </x:c>
       <x:c r="D47" s="16" t="str">
-        <x:v>Express app is available</x:v>
+        <x:v>Valid TXT and unsupported file</x:v>
       </x:c>
       <x:c r="E47" s="16" t="str">
-        <x:v>Invalid JSON body shape</x:v>
+        <x:v>Two multipart files</x:v>
       </x:c>
       <x:c r="F47" s="16" t="str">
-        <x:v>POST /api/report.</x:v>
+        <x:v>POST /api/analyze.</x:v>
       </x:c>
       <x:c r="G47" s="16" t="str">
-        <x:v>HTTP 400 returns a safe validation error with no stack trace.</x:v>
+        <x:v>Valid result is preserved and unsupported file is reported independently.</x:v>
       </x:c>
       <x:c r="H47" s="16" t="str">
-        <x:v>tests/api/report-api.test.ts — rejects malformed report requests without a stack trace</x:v>
+        <x:v>tests/api/analyze-api.test.ts — preserves valid results when another uploaded file is unsupported</x:v>
       </x:c>
       <x:c r="I47" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1738,28 +1738,28 @@
     </x:row>
     <x:row r="48" ht="62" customHeight="1">
       <x:c r="A48" s="16" t="str">
-        <x:v>IT-RPT-001</x:v>
+        <x:v>IT-API-003</x:v>
       </x:c>
       <x:c r="B48" s="16" t="str">
-        <x:v>Report API</x:v>
+        <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C48" s="16" t="str">
-        <x:v>Word report export</x:v>
+        <x:v>Empty file isolation</x:v>
       </x:c>
       <x:c r="D48" s="16" t="str">
-        <x:v>Valid analysis batch</x:v>
+        <x:v>Valid TXT and empty TXT</x:v>
       </x:c>
       <x:c r="E48" s="16" t="str">
-        <x:v>POST /api/report</x:v>
+        <x:v>Two multipart files</x:v>
       </x:c>
       <x:c r="F48" s="16" t="str">
-        <x:v>Generate and inspect returned ZIP.</x:v>
+        <x:v>POST /api/analyze.</x:v>
       </x:c>
       <x:c r="G48" s="16" t="str">
-        <x:v>DOCX OOXML contains actual meeting results.</x:v>
+        <x:v>Valid meeting succeeds and empty file has its own failure.</x:v>
       </x:c>
       <x:c r="H48" s="16" t="str">
-        <x:v>tests/api/report-api.test.ts — returns a readable Word OOXML report containing actual results</x:v>
+        <x:v>tests/api/analyze-api.test.ts — reports an empty file independently while processing another file</x:v>
       </x:c>
       <x:c r="I48" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1767,28 +1767,28 @@
     </x:row>
     <x:row r="49" ht="62" customHeight="1">
       <x:c r="A49" s="16" t="str">
-        <x:v>CT-UI-001</x:v>
+        <x:v>IT-API-004</x:v>
       </x:c>
       <x:c r="B49" s="16" t="str">
-        <x:v>Frontend</x:v>
+        <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C49" s="16" t="str">
-        <x:v>Additive deduplicated file queue</x:v>
+        <x:v>Health endpoint</x:v>
       </x:c>
       <x:c r="D49" s="16" t="str">
-        <x:v>Application rendered</x:v>
+        <x:v>Express app is available</x:v>
       </x:c>
       <x:c r="E49" s="16" t="str">
-        <x:v>Two file-selection rounds with a duplicate</x:v>
+        <x:v>GET /api/health</x:v>
       </x:c>
       <x:c r="F49" s="16" t="str">
-        <x:v>Select files; click Analyze Meetings.</x:v>
+        <x:v>Request service readiness.</x:v>
       </x:c>
       <x:c r="G49" s="16" t="str">
-        <x:v>Unique files remain queued and analysis starts only on explicit click.</x:v>
+        <x:v>HTTP 200 reports ready without internal implementation details.</x:v>
       </x:c>
       <x:c r="H49" s="16" t="str">
-        <x:v>tests/frontend/app.test.tsx — adds files across selection rounds, avoids duplicates, and analyzes explicitly</x:v>
+        <x:v>tests/api/analyze-api.test.ts — reports service readiness without exposing internals</x:v>
       </x:c>
       <x:c r="I49" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1796,28 +1796,28 @@
     </x:row>
     <x:row r="50" ht="62" customHeight="1">
       <x:c r="A50" s="16" t="str">
-        <x:v>CT-UI-002</x:v>
+        <x:v>IT-API-005</x:v>
       </x:c>
       <x:c r="B50" s="16" t="str">
-        <x:v>Frontend</x:v>
+        <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C50" s="16" t="str">
-        <x:v>Accessible empty state</x:v>
+        <x:v>Oversized file isolation</x:v>
       </x:c>
       <x:c r="D50" s="16" t="str">
-        <x:v>Application rendered with no files</x:v>
+        <x:v>Valid TXT and a TXT over 1 MiB</x:v>
       </x:c>
       <x:c r="E50" s="16" t="str">
-        <x:v>No interaction</x:v>
+        <x:v>Two multipart files</x:v>
       </x:c>
       <x:c r="F50" s="16" t="str">
-        <x:v>Inspect upload and analysis controls.</x:v>
+        <x:v>POST /api/analyze.</x:v>
       </x:c>
       <x:c r="G50" s="16" t="str">
-        <x:v>Empty-state guidance is visible and analysis action is disabled.</x:v>
+        <x:v>Valid meeting succeeds and oversized file receives file-too-large failure.</x:v>
       </x:c>
       <x:c r="H50" s="16" t="str">
-        <x:v>tests/frontend/app.test.tsx — starts with an accessible empty upload state and disabled analysis action</x:v>
+        <x:v>tests/api/analyze-api.test.ts — keeps valid results when another text file exceeds the application limit</x:v>
       </x:c>
       <x:c r="I50" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1825,28 +1825,28 @@
     </x:row>
     <x:row r="51" ht="62" customHeight="1">
       <x:c r="A51" s="16" t="str">
-        <x:v>CT-UI-003</x:v>
+        <x:v>IT-API-006</x:v>
       </x:c>
       <x:c r="B51" s="16" t="str">
-        <x:v>Frontend</x:v>
+        <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C51" s="16" t="str">
-        <x:v>Client-side unsupported file feedback</x:v>
+        <x:v>Invalid UTF-8 isolation</x:v>
       </x:c>
       <x:c r="D51" s="16" t="str">
-        <x:v>Application rendered</x:v>
+        <x:v>Valid TXT and invalid byte sequence</x:v>
       </x:c>
       <x:c r="E51" s="16" t="str">
-        <x:v>notes.pdf</x:v>
+        <x:v>Two multipart files</x:v>
       </x:c>
       <x:c r="F51" s="16" t="str">
-        <x:v>Select unsupported file.</x:v>
+        <x:v>POST /api/analyze.</x:v>
       </x:c>
       <x:c r="G51" s="16" t="str">
-        <x:v>Visible useful feedback appears before an upload request.</x:v>
+        <x:v>Valid meeting succeeds and invalid text receives invalid-upload failure.</x:v>
       </x:c>
       <x:c r="H51" s="16" t="str">
-        <x:v>tests/frontend/app.test.tsx — rejects unsupported files before upload and shows useful feedback</x:v>
+        <x:v>tests/api/analyze-api.test.ts — reports invalid UTF-8 as a per-file upload failure</x:v>
       </x:c>
       <x:c r="I51" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1854,28 +1854,28 @@
     </x:row>
     <x:row r="52" ht="62" customHeight="1">
       <x:c r="A52" s="16" t="str">
-        <x:v>AT-DOC-001</x:v>
+        <x:v>IT-API-007</x:v>
       </x:c>
       <x:c r="B52" s="16" t="str">
-        <x:v>Submission artifacts</x:v>
+        <x:v>Analysis API</x:v>
       </x:c>
       <x:c r="C52" s="16" t="str">
-        <x:v>SRS OOXML integrity</x:v>
+        <x:v>Prototype-safe owner grouping</x:v>
       </x:c>
       <x:c r="D52" s="16" t="str">
-        <x:v>Generated SRS exists</x:v>
+        <x:v>Owner name is Constructor</x:v>
       </x:c>
       <x:c r="E52" s="16" t="str">
-        <x:v>Meeting_Notes_Distiller_SRS.docx</x:v>
+        <x:v>Constructor: I will prepare the release notes Friday.</x:v>
       </x:c>
       <x:c r="F52" s="16" t="str">
-        <x:v>Open ZIP entries; inspect document XML.</x:v>
+        <x:v>POST /api/analyze; inspect groupedActionItems.</x:v>
       </x:c>
       <x:c r="G52" s="16" t="str">
-        <x:v>Valid Word package contains required implemented-requirement sections.</x:v>
+        <x:v>Constructor group contains the action and request succeeds.</x:v>
       </x:c>
       <x:c r="H52" s="16" t="str">
-        <x:v>tests/artifacts/submission-documents.test.ts — includes a valid SRS Word document with implemented requirements</x:v>
+        <x:v>tests/api/analyze-api.test.ts — groups an owner whose name matches an object prototype property</x:v>
       </x:c>
       <x:c r="I52" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1883,28 +1883,28 @@
     </x:row>
     <x:row r="53" ht="62" customHeight="1">
       <x:c r="A53" s="16" t="str">
-        <x:v>AT-XLS-001</x:v>
+        <x:v>IT-API-008</x:v>
       </x:c>
       <x:c r="B53" s="16" t="str">
-        <x:v>Submission artifacts</x:v>
+        <x:v>HTTP boundary</x:v>
       </x:c>
       <x:c r="C53" s="16" t="str">
-        <x:v>Unit test workbook integrity</x:v>
+        <x:v>Same-origin policy</x:v>
       </x:c>
       <x:c r="D53" s="16" t="str">
-        <x:v>Generated workbook exists</x:v>
+        <x:v>Health endpoint available</x:v>
       </x:c>
       <x:c r="E53" s="16" t="str">
-        <x:v>Unit_Test_Cases.xlsx</x:v>
+        <x:v>GET with attacker Origin header</x:v>
       </x:c>
       <x:c r="F53" s="16" t="str">
-        <x:v>Open ZIP entries; inspect workbook and cell XML.</x:v>
+        <x:v>Request /api/health.</x:v>
       </x:c>
       <x:c r="G53" s="16" t="str">
-        <x:v>Valid Excel package contains both mandatory edge-case scenarios.</x:v>
+        <x:v>Response does not grant Access-Control-Allow-Origin.</x:v>
       </x:c>
       <x:c r="H53" s="16" t="str">
-        <x:v>tests/artifacts/submission-documents.test.ts — includes a valid test-case workbook at docs/Unit_Test_Cases.xlsx</x:v>
+        <x:v>tests/api/analyze-api.test.ts — does not opt arbitrary third-party origins into CORS</x:v>
       </x:c>
       <x:c r="I53" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1912,28 +1912,28 @@
     </x:row>
     <x:row r="54" ht="62" customHeight="1">
       <x:c r="A54" s="16" t="str">
-        <x:v>AT-XLS-002</x:v>
+        <x:v>IT-RPT-000</x:v>
       </x:c>
       <x:c r="B54" s="16" t="str">
-        <x:v>Submission artifacts</x:v>
+        <x:v>Report API</x:v>
       </x:c>
       <x:c r="C54" s="16" t="str">
-        <x:v>SIT/UAT workbook integrity</x:v>
+        <x:v>Malformed report request</x:v>
       </x:c>
       <x:c r="D54" s="16" t="str">
-        <x:v>Generated workbook exists</x:v>
+        <x:v>Express app is available</x:v>
       </x:c>
       <x:c r="E54" s="16" t="str">
-        <x:v>SIT_UAT_Test_Cases.xlsx</x:v>
+        <x:v>Invalid JSON body shape</x:v>
       </x:c>
       <x:c r="F54" s="16" t="str">
-        <x:v>Open ZIP entries; inspect workbook and cell XML.</x:v>
+        <x:v>POST /api/report.</x:v>
       </x:c>
       <x:c r="G54" s="16" t="str">
-        <x:v>Valid Excel package contains upload and report workflows.</x:v>
+        <x:v>HTTP 400 returns a safe validation error with no stack trace.</x:v>
       </x:c>
       <x:c r="H54" s="16" t="str">
-        <x:v>tests/artifacts/submission-documents.test.ts — includes a valid test-case workbook at docs/SIT_UAT_Test_Cases.xlsx</x:v>
+        <x:v>tests/api/report-api.test.ts — rejects malformed report requests without a stack trace</x:v>
       </x:c>
       <x:c r="I54" s="24" t="str">
         <x:v>PASS</x:v>
@@ -1941,30 +1941,262 @@
     </x:row>
     <x:row r="55" ht="62" customHeight="1">
       <x:c r="A55" s="16" t="str">
+        <x:v>IT-RPT-001</x:v>
+      </x:c>
+      <x:c r="B55" s="16" t="str">
+        <x:v>Report API</x:v>
+      </x:c>
+      <x:c r="C55" s="16" t="str">
+        <x:v>Word report export</x:v>
+      </x:c>
+      <x:c r="D55" s="16" t="str">
+        <x:v>Valid analysis batch</x:v>
+      </x:c>
+      <x:c r="E55" s="16" t="str">
+        <x:v>POST /api/report</x:v>
+      </x:c>
+      <x:c r="F55" s="16" t="str">
+        <x:v>Generate and inspect returned ZIP.</x:v>
+      </x:c>
+      <x:c r="G55" s="16" t="str">
+        <x:v>DOCX OOXML contains actual meeting results.</x:v>
+      </x:c>
+      <x:c r="H55" s="16" t="str">
+        <x:v>tests/api/report-api.test.ts — returns a readable Word OOXML report containing actual results</x:v>
+      </x:c>
+      <x:c r="I55" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="62" customHeight="1">
+      <x:c r="A56" s="16" t="str">
+        <x:v>CT-UI-001</x:v>
+      </x:c>
+      <x:c r="B56" s="16" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="C56" s="16" t="str">
+        <x:v>Additive deduplicated file queue</x:v>
+      </x:c>
+      <x:c r="D56" s="16" t="str">
+        <x:v>Application rendered</x:v>
+      </x:c>
+      <x:c r="E56" s="16" t="str">
+        <x:v>Two file-selection rounds with a duplicate</x:v>
+      </x:c>
+      <x:c r="F56" s="16" t="str">
+        <x:v>Select files; click Analyze Meetings.</x:v>
+      </x:c>
+      <x:c r="G56" s="16" t="str">
+        <x:v>Unique files remain queued and analysis starts only on explicit click.</x:v>
+      </x:c>
+      <x:c r="H56" s="16" t="str">
+        <x:v>tests/frontend/app.test.tsx — adds files across selection rounds, avoids duplicates, and analyzes explicitly</x:v>
+      </x:c>
+      <x:c r="I56" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="62" customHeight="1">
+      <x:c r="A57" s="16" t="str">
+        <x:v>CT-UI-002</x:v>
+      </x:c>
+      <x:c r="B57" s="16" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="C57" s="16" t="str">
+        <x:v>Accessible empty state</x:v>
+      </x:c>
+      <x:c r="D57" s="16" t="str">
+        <x:v>Application rendered with no files</x:v>
+      </x:c>
+      <x:c r="E57" s="16" t="str">
+        <x:v>No interaction</x:v>
+      </x:c>
+      <x:c r="F57" s="16" t="str">
+        <x:v>Inspect upload and analysis controls.</x:v>
+      </x:c>
+      <x:c r="G57" s="16" t="str">
+        <x:v>Empty-state guidance is visible and analysis action is disabled.</x:v>
+      </x:c>
+      <x:c r="H57" s="16" t="str">
+        <x:v>tests/frontend/app.test.tsx — starts with an accessible empty upload state and disabled analysis action</x:v>
+      </x:c>
+      <x:c r="I57" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="62" customHeight="1">
+      <x:c r="A58" s="16" t="str">
+        <x:v>CT-UI-003</x:v>
+      </x:c>
+      <x:c r="B58" s="16" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="C58" s="16" t="str">
+        <x:v>Client-side unsupported file feedback</x:v>
+      </x:c>
+      <x:c r="D58" s="16" t="str">
+        <x:v>Application rendered</x:v>
+      </x:c>
+      <x:c r="E58" s="16" t="str">
+        <x:v>notes.pdf</x:v>
+      </x:c>
+      <x:c r="F58" s="16" t="str">
+        <x:v>Select unsupported file.</x:v>
+      </x:c>
+      <x:c r="G58" s="16" t="str">
+        <x:v>Visible useful feedback appears before an upload request.</x:v>
+      </x:c>
+      <x:c r="H58" s="16" t="str">
+        <x:v>tests/frontend/app.test.tsx — rejects unsupported files before upload and shows useful feedback</x:v>
+      </x:c>
+      <x:c r="I58" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="62" customHeight="1">
+      <x:c r="A59" s="16" t="str">
+        <x:v>CT-UI-004</x:v>
+      </x:c>
+      <x:c r="B59" s="16" t="str">
+        <x:v>Frontend</x:v>
+      </x:c>
+      <x:c r="C59" s="16" t="str">
+        <x:v>Single-card multi-meeting navigation</x:v>
+      </x:c>
+      <x:c r="D59" s="16" t="str">
+        <x:v>Two meeting analyses are available</x:v>
+      </x:c>
+      <x:c r="E59" s="16" t="str">
+        <x:v>launch.txt and tasks.txt</x:v>
+      </x:c>
+      <x:c r="F59" s="16" t="str">
+        <x:v>Analyze; inspect progress; select the second file; use Previous.</x:v>
+      </x:c>
+      <x:c r="G59" s="16" t="str">
+        <x:v>Meeting position updates and exactly one selected meeting detail card is visible.</x:v>
+      </x:c>
+      <x:c r="H59" s="16" t="str">
+        <x:v>tests/frontend/app.test.tsx — shows one meeting card at a time and navigates between uploaded files</x:v>
+      </x:c>
+      <x:c r="I59" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="62" customHeight="1">
+      <x:c r="A60" s="16" t="str">
+        <x:v>AT-DOC-001</x:v>
+      </x:c>
+      <x:c r="B60" s="16" t="str">
+        <x:v>Submission artifacts</x:v>
+      </x:c>
+      <x:c r="C60" s="16" t="str">
+        <x:v>SRS OOXML integrity</x:v>
+      </x:c>
+      <x:c r="D60" s="16" t="str">
+        <x:v>Generated SRS exists</x:v>
+      </x:c>
+      <x:c r="E60" s="16" t="str">
+        <x:v>Meeting_Notes_Distiller_SRS.docx</x:v>
+      </x:c>
+      <x:c r="F60" s="16" t="str">
+        <x:v>Open ZIP entries; inspect document XML.</x:v>
+      </x:c>
+      <x:c r="G60" s="16" t="str">
+        <x:v>Valid Word package contains required implemented-requirement sections.</x:v>
+      </x:c>
+      <x:c r="H60" s="16" t="str">
+        <x:v>tests/artifacts/submission-documents.test.ts — includes a valid SRS Word document with implemented requirements</x:v>
+      </x:c>
+      <x:c r="I60" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="62" customHeight="1">
+      <x:c r="A61" s="16" t="str">
+        <x:v>AT-XLS-001</x:v>
+      </x:c>
+      <x:c r="B61" s="16" t="str">
+        <x:v>Submission artifacts</x:v>
+      </x:c>
+      <x:c r="C61" s="16" t="str">
+        <x:v>Unit test workbook integrity</x:v>
+      </x:c>
+      <x:c r="D61" s="16" t="str">
+        <x:v>Generated workbook exists</x:v>
+      </x:c>
+      <x:c r="E61" s="16" t="str">
+        <x:v>Unit_Test_Cases.xlsx</x:v>
+      </x:c>
+      <x:c r="F61" s="16" t="str">
+        <x:v>Open ZIP entries; inspect workbook and cell XML.</x:v>
+      </x:c>
+      <x:c r="G61" s="16" t="str">
+        <x:v>Valid Excel package contains both mandatory edge-case scenarios.</x:v>
+      </x:c>
+      <x:c r="H61" s="16" t="str">
+        <x:v>tests/artifacts/submission-documents.test.ts — includes a valid test-case workbook at docs/Unit_Test_Cases.xlsx</x:v>
+      </x:c>
+      <x:c r="I61" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="62" customHeight="1">
+      <x:c r="A62" s="16" t="str">
+        <x:v>AT-XLS-002</x:v>
+      </x:c>
+      <x:c r="B62" s="16" t="str">
+        <x:v>Submission artifacts</x:v>
+      </x:c>
+      <x:c r="C62" s="16" t="str">
+        <x:v>SIT/UAT workbook integrity</x:v>
+      </x:c>
+      <x:c r="D62" s="16" t="str">
+        <x:v>Generated workbook exists</x:v>
+      </x:c>
+      <x:c r="E62" s="16" t="str">
+        <x:v>SIT_UAT_Test_Cases.xlsx</x:v>
+      </x:c>
+      <x:c r="F62" s="16" t="str">
+        <x:v>Open ZIP entries; inspect workbook and cell XML.</x:v>
+      </x:c>
+      <x:c r="G62" s="16" t="str">
+        <x:v>Valid Excel package contains upload and report workflows.</x:v>
+      </x:c>
+      <x:c r="H62" s="16" t="str">
+        <x:v>tests/artifacts/submission-documents.test.ts — includes a valid test-case workbook at docs/SIT_UAT_Test_Cases.xlsx</x:v>
+      </x:c>
+      <x:c r="I62" s="24" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="62" customHeight="1">
+      <x:c r="A63" s="16" t="str">
         <x:v>AT-CAT-001</x:v>
       </x:c>
-      <x:c r="B55" s="16" t="str">
+      <x:c r="B63" s="16" t="str">
         <x:v>Submission artifacts</x:v>
       </x:c>
-      <x:c r="C55" s="16" t="str">
+      <x:c r="C63" s="16" t="str">
         <x:v>Test catalog synchronization</x:v>
       </x:c>
-      <x:c r="D55" s="16" t="str">
+      <x:c r="D63" s="16" t="str">
         <x:v>Catalog and test sources exist</x:v>
       </x:c>
-      <x:c r="E55" s="16" t="str">
+      <x:c r="E63" s="16" t="str">
         <x:v>scripts/test-catalog.mjs</x:v>
       </x:c>
-      <x:c r="F55" s="16" t="str">
+      <x:c r="F63" s="16" t="str">
         <x:v>Check all suite source paths are referenced.</x:v>
       </x:c>
-      <x:c r="G55" s="16" t="str">
+      <x:c r="G63" s="16" t="str">
         <x:v>Catalog remains linked to unit, API, component, artifact, and E2E source files.</x:v>
       </x:c>
-      <x:c r="H55" s="16" t="str">
+      <x:c r="H63" s="16" t="str">
         <x:v>tests/artifacts/submission-documents.test.ts — keeps the documented test catalog synchronized with test source references</x:v>
       </x:c>
-      <x:c r="I55" s="24" t="str">
+      <x:c r="I63" s="24" t="str">
         <x:v>PASS</x:v>
       </x:c>
     </x:row>
@@ -1976,7 +2208,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8a620abd52546e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9125d0347354c82"/>
   </x:tableParts>
 </x:worksheet>
 </file>